--- a/config/data/EnemyTemplate.xlsx
+++ b/config/data/EnemyTemplate.xlsx
@@ -1,112 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="EnemyTemplate" sheetId="1" r:id="rId1"/>
+    <sheet name="EnemyTemplate" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="25">
-  <si>
-    <t>@table</t>
-  </si>
-  <si>
-    <t>EnemyTemplate</t>
-  </si>
-  <si>
-    <t>@mode</t>
-  </si>
-  <si>
-    <t>map</t>
-  </si>
-  <si>
-    <t>@key</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
-  </si>
-  <si>
-    <t>@schema</t>
-  </si>
-  <si>
-    <t>1a5340995b67d6bd</t>
-  </si>
-  <si>
-    <t>#name</t>
-  </si>
-  <si>
-    <t>rank</t>
-  </si>
-  <si>
-    <t>base_aggro_decimal</t>
-  </si>
-  <si>
-    <t>default_ai_graph_id</t>
-  </si>
-  <si>
-    <t>#field</t>
-  </si>
-  <si>
-    <t>#type</t>
-  </si>
-  <si>
-    <t>ref&lt;ContentIdentity.id&gt;</t>
-  </si>
-  <si>
-    <t>enum&lt;EnemyRank&gt;</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>ref&lt;AiGraph.id&gt;</t>
-  </si>
-  <si>
-    <t>#scope</t>
-  </si>
-  <si>
-    <t>#input</t>
-  </si>
-  <si>
-    <t>key</t>
-  </si>
-  <si>
-    <t>length=1..32</t>
-  </si>
-  <si>
-    <t>#desc</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -125,13 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -419,124 +407,502 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>24</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>EnemyTemplate</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>@scope</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>1a5340995b67d6bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>base_aggro_decimal</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>default_ai_graph_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>base_aggro_decimal</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>default_ai_graph_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ref&lt;ContentIdentity.id&gt;</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>enum&lt;EnemyRank&gt;</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ref&lt;AiGraph.id&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>#scope</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>length=1..32</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>10001</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>13001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>10002</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>13002</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>10003</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>13003</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>10004</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>13004</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>10005</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>13005</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>10006</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>13006</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>10007</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>13007</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>10008</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>13008</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>10009</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Minion</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>13009</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>10010</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Minion</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>13010</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>10011</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>13011</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>10012</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>13012</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>10013</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>13013</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>10014</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>13014</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>10015</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>13015</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>10016</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>13016</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>10017</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>13017</v>
       </c>
     </row>
   </sheetData>

--- a/config/data/EnemyTemplate.xlsx
+++ b/config/data/EnemyTemplate.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -905,6 +905,24 @@
         <v>13017</v>
       </c>
     </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>980002</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>980010</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyTemplate.xlsx
+++ b/config/data/EnemyTemplate.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,6 +923,24 @@
         <v>980010</v>
       </c>
     </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>990002</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>990010</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyTemplate.xlsx
+++ b/config/data/EnemyTemplate.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -941,6 +941,24 @@
         <v>990010</v>
       </c>
     </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>1000002</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1000010</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyTemplate.xlsx
+++ b/config/data/EnemyTemplate.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -959,6 +959,24 @@
         <v>1000010</v>
       </c>
     </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>1010002</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1010010</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyTemplate.xlsx
+++ b/config/data/EnemyTemplate.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -977,6 +977,24 @@
         <v>1010010</v>
       </c>
     </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>1020002</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1020010</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyTemplate.xlsx
+++ b/config/data/EnemyTemplate.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -995,6 +995,24 @@
         <v>1020010</v>
       </c>
     </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>1030002</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1030010</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyTemplate.xlsx
+++ b/config/data/EnemyTemplate.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1013,6 +1013,24 @@
         <v>1030010</v>
       </c>
     </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>1040002</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1040010</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyTemplate.xlsx
+++ b/config/data/EnemyTemplate.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1031,6 +1031,24 @@
         <v>1040010</v>
       </c>
     </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>1050002</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1050010</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyTemplate.xlsx
+++ b/config/data/EnemyTemplate.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1049,6 +1049,24 @@
         <v>1050010</v>
       </c>
     </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>1060002</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1060010</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyTemplate.xlsx
+++ b/config/data/EnemyTemplate.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1067,6 +1067,24 @@
         <v>1060010</v>
       </c>
     </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>1070002</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1070010</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyTemplate.xlsx
+++ b/config/data/EnemyTemplate.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1085,6 +1085,24 @@
         <v>1070010</v>
       </c>
     </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>1080002</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1080010</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyTemplate.xlsx
+++ b/config/data/EnemyTemplate.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,7 +601,7 @@
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>10001</v>
+        <v>10003</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>13001</v>
+        <v>13003</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>10002</v>
+        <v>10004</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -632,12 +632,12 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>13002</v>
+        <v>13004</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>10003</v>
+        <v>10005</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -650,16 +650,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>13003</v>
+        <v>13005</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>10004</v>
+        <v>10006</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -668,12 +668,12 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13004</v>
+        <v>13006</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>10005</v>
+        <v>10007</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>13005</v>
+        <v>13007</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>10006</v>
+        <v>10008</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -704,16 +704,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>13006</v>
+        <v>13008</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>10007</v>
+        <v>10009</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -722,16 +722,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>13007</v>
+        <v>13009</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>10008</v>
+        <v>10010</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -740,16 +740,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>13008</v>
+        <v>13010</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>10009</v>
+        <v>10011</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -758,16 +758,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>13009</v>
+        <v>13011</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>10010</v>
+        <v>10012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -776,16 +776,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>13010</v>
+        <v>13012</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>10011</v>
+        <v>10013</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -794,12 +794,12 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>13011</v>
+        <v>13013</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>10012</v>
+        <v>10014</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -812,12 +812,12 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>13012</v>
+        <v>13014</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>10013</v>
+        <v>10015</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -830,12 +830,12 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>13013</v>
+        <v>13015</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>10014</v>
+        <v>10016</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -848,16 +848,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>13014</v>
+        <v>13016</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>10015</v>
+        <v>10017</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -866,16 +866,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>13015</v>
+        <v>13017</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>10016</v>
+        <v>980002</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -884,12 +884,12 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>13016</v>
+        <v>980010</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>10017</v>
+        <v>990002</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -902,16 +902,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>13017</v>
+        <v>990010</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>980002</v>
+        <v>1000002</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -920,12 +920,12 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>980010</v>
+        <v>1000010</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>990002</v>
+        <v>1010002</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -938,16 +938,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>990010</v>
+        <v>1010010</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>1000002</v>
+        <v>1020002</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -956,16 +956,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1000010</v>
+        <v>1020010</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>1010002</v>
+        <v>1030002</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -974,12 +974,12 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1010010</v>
+        <v>1030010</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>1020002</v>
+        <v>1040002</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1020010</v>
+        <v>1040010</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>1030002</v>
+        <v>1050002</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1010,12 +1010,12 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1030010</v>
+        <v>1050010</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>1040002</v>
+        <v>1060002</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1028,16 +1028,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1040010</v>
+        <v>1060010</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>1050002</v>
+        <v>1070002</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1046,12 +1046,12 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1050010</v>
+        <v>1070010</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>1060002</v>
+        <v>1080002</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1064,16 +1064,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1060010</v>
+        <v>1080010</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>1070002</v>
+        <v>10001</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1082,16 +1082,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1070010</v>
+        <v>1090041</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>1080002</v>
+        <v>1090022</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1100,7 +1100,187 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1080010</v>
+        <v>1090042</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>1090023</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1090043</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>1090024</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1090044</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>1090025</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Minion</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1090045</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>1090026</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1090046</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>10002</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1090047</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>1090028</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1090048</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>1090029</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1090049</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>1090030</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1090050</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>1090031</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1090051</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>1090032</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1090052</v>
       </c>
     </row>
   </sheetData>

--- a/config/data/EnemyTemplate.xlsx
+++ b/config/data/EnemyTemplate.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,11 +601,11 @@
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>10003</v>
+        <v>10004</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>13003</v>
+        <v>13004</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>10004</v>
+        <v>10007</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -632,12 +632,12 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>13004</v>
+        <v>13007</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>10005</v>
+        <v>10008</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -650,16 +650,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>13005</v>
+        <v>13008</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>10006</v>
+        <v>10009</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -668,16 +668,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13006</v>
+        <v>13009</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>10007</v>
+        <v>10010</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>13007</v>
+        <v>13010</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>10008</v>
+        <v>10011</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -704,16 +704,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>13008</v>
+        <v>13011</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>10009</v>
+        <v>10012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -722,16 +722,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>13009</v>
+        <v>13012</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>10010</v>
+        <v>10013</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -740,16 +740,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>13010</v>
+        <v>13013</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>10011</v>
+        <v>10014</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -758,12 +758,12 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>13011</v>
+        <v>13014</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>10012</v>
+        <v>10015</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -776,12 +776,12 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>13012</v>
+        <v>13015</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>10013</v>
+        <v>10016</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -794,16 +794,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>13013</v>
+        <v>13016</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>10014</v>
+        <v>10017</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>13014</v>
+        <v>13017</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>10015</v>
+        <v>980002</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -830,16 +830,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>13015</v>
+        <v>980010</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>10016</v>
+        <v>990002</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -848,12 +848,12 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>13016</v>
+        <v>990010</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>10017</v>
+        <v>1000002</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -866,16 +866,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>13017</v>
+        <v>1000010</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>980002</v>
+        <v>1010002</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -884,16 +884,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>980010</v>
+        <v>1010010</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>990002</v>
+        <v>1020002</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -902,16 +902,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>990010</v>
+        <v>1020010</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>1000002</v>
+        <v>1030002</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -920,16 +920,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1000010</v>
+        <v>1030010</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>1010002</v>
+        <v>1040002</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -938,16 +938,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1010010</v>
+        <v>1040010</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>1020002</v>
+        <v>1050002</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -956,12 +956,12 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1020010</v>
+        <v>1050010</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>1030002</v>
+        <v>1060002</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -974,12 +974,12 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1030010</v>
+        <v>1060010</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>1040002</v>
+        <v>1070002</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1040010</v>
+        <v>1070010</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>1050002</v>
+        <v>1080002</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1010,16 +1010,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1050010</v>
+        <v>1080010</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>1060002</v>
+        <v>10001</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1028,16 +1028,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1060010</v>
+        <v>1090041</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>1070002</v>
+        <v>1090022</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1046,16 +1046,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1070010</v>
+        <v>1090042</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>1080002</v>
+        <v>1090023</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1064,12 +1064,12 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1080010</v>
+        <v>1090043</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>10001</v>
+        <v>1090024</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1090041</v>
+        <v>1090044</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>1090022</v>
+        <v>1090025</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1100,12 +1100,12 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1090042</v>
+        <v>1090045</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>1090023</v>
+        <v>1090026</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1118,16 +1118,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1090043</v>
+        <v>1090046</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>1090024</v>
+        <v>10002</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1136,16 +1136,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1090044</v>
+        <v>1090047</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>1090025</v>
+        <v>1090028</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1154,16 +1154,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1090045</v>
+        <v>1090048</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>1090026</v>
+        <v>1090029</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1172,12 +1172,12 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1090046</v>
+        <v>1090049</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>10002</v>
+        <v>1090030</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1190,12 +1190,12 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1090047</v>
+        <v>1090050</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>1090028</v>
+        <v>1090031</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1208,12 +1208,12 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1090048</v>
+        <v>1090051</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>1090029</v>
+        <v>1090032</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1226,16 +1226,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1090049</v>
+        <v>1090052</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>1090030</v>
+        <v>10003</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1244,16 +1244,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1090050</v>
+        <v>1100041</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>1090031</v>
+        <v>1100022</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1262,12 +1262,12 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1090051</v>
+        <v>1100042</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>1090032</v>
+        <v>1100023</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1280,7 +1280,169 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1090052</v>
+        <v>1100043</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>1100024</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1100044</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>10005</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1100045</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>1100026</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1100046</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>1100027</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1100047</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>10006</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1100048</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>1100029</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1100049</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>1100030</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1100050</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>1100031</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Minion</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1100051</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>1100032</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1100052</v>
       </c>
     </row>
   </sheetData>

--- a/config/data/EnemyTemplate.xlsx
+++ b/config/data/EnemyTemplate.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -637,11 +637,11 @@
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>10008</v>
+        <v>10011</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -650,16 +650,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>13008</v>
+        <v>13011</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>10009</v>
+        <v>10012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -668,16 +668,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13009</v>
+        <v>13012</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>10010</v>
+        <v>10013</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>13010</v>
+        <v>13013</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>10011</v>
+        <v>10014</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -704,12 +704,12 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>13011</v>
+        <v>13014</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>10012</v>
+        <v>10015</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -722,12 +722,12 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>13012</v>
+        <v>13015</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>10013</v>
+        <v>10016</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -740,16 +740,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>13013</v>
+        <v>13016</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>10014</v>
+        <v>10017</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -758,16 +758,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>13014</v>
+        <v>13017</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>10015</v>
+        <v>980002</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -776,16 +776,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>13015</v>
+        <v>980010</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>10016</v>
+        <v>990002</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -794,12 +794,12 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>13016</v>
+        <v>990010</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>10017</v>
+        <v>1000002</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>13017</v>
+        <v>1000010</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>980002</v>
+        <v>1010002</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -830,16 +830,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>980010</v>
+        <v>1010010</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>990002</v>
+        <v>1020002</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -848,16 +848,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>990010</v>
+        <v>1020010</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>1000002</v>
+        <v>1030002</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -866,16 +866,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1000010</v>
+        <v>1030010</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>1010002</v>
+        <v>1040002</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -884,16 +884,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1010010</v>
+        <v>1040010</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>1020002</v>
+        <v>1050002</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -902,12 +902,12 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1020010</v>
+        <v>1050010</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>1030002</v>
+        <v>1060002</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -920,12 +920,12 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1030010</v>
+        <v>1060010</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>1040002</v>
+        <v>1070002</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -938,16 +938,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1040010</v>
+        <v>1070010</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>1050002</v>
+        <v>1080002</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -956,16 +956,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1050010</v>
+        <v>1080010</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>1060002</v>
+        <v>10001</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -974,16 +974,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1060010</v>
+        <v>1090041</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>1070002</v>
+        <v>1090022</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -992,16 +992,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1070010</v>
+        <v>1090042</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>1080002</v>
+        <v>1090023</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1010,12 +1010,12 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1080010</v>
+        <v>1090043</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>10001</v>
+        <v>1090024</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1028,16 +1028,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1090041</v>
+        <v>1090044</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>1090022</v>
+        <v>1090025</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1046,12 +1046,12 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1090042</v>
+        <v>1090045</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>1090023</v>
+        <v>1090026</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1064,16 +1064,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1090043</v>
+        <v>1090046</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>1090024</v>
+        <v>10002</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1082,16 +1082,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1090044</v>
+        <v>1090047</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>1090025</v>
+        <v>1090028</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1100,16 +1100,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1090045</v>
+        <v>1090048</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>1090026</v>
+        <v>1090029</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1118,12 +1118,12 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1090046</v>
+        <v>1090049</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>10002</v>
+        <v>1090030</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1136,12 +1136,12 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1090047</v>
+        <v>1090050</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>1090028</v>
+        <v>1090031</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1154,12 +1154,12 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1090048</v>
+        <v>1090051</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>1090029</v>
+        <v>1090032</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1172,16 +1172,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1090049</v>
+        <v>1090052</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>1090030</v>
+        <v>10003</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1190,16 +1190,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1090050</v>
+        <v>1100041</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>1090031</v>
+        <v>1100022</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1208,12 +1208,12 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1090051</v>
+        <v>1100042</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>1090032</v>
+        <v>1100023</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1226,16 +1226,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1090052</v>
+        <v>1100043</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>10003</v>
+        <v>1100024</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1244,16 +1244,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1100041</v>
+        <v>1100044</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>1100022</v>
+        <v>10005</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1262,12 +1262,12 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1100042</v>
+        <v>1100045</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>1100023</v>
+        <v>1100026</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1280,12 +1280,12 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1100043</v>
+        <v>1100046</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>1100024</v>
+        <v>1100027</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1298,16 +1298,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1100044</v>
+        <v>1100047</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="n">
-        <v>10005</v>
+        <v>10006</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1316,16 +1316,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1100045</v>
+        <v>1100048</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="n">
-        <v>1100026</v>
+        <v>1100029</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1334,12 +1334,12 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1100046</v>
+        <v>1100049</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>1100027</v>
+        <v>1100030</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1352,16 +1352,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1100047</v>
+        <v>1100050</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>10006</v>
+        <v>1100031</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1370,16 +1370,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1100048</v>
+        <v>1100051</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="n">
-        <v>1100029</v>
+        <v>1100032</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1388,16 +1388,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1100049</v>
+        <v>1100052</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="n">
-        <v>1100030</v>
+        <v>1110021</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1406,12 +1406,12 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1100050</v>
+        <v>1110041</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="n">
-        <v>1100031</v>
+        <v>1110022</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1424,16 +1424,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1100051</v>
+        <v>1110042</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" t="n">
-        <v>1100032</v>
+        <v>1110023</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1442,7 +1442,169 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1100052</v>
+        <v>1110043</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>1110024</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1110044</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>1110025</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1110045</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>1110026</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Minion</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1110046</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>10008</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>1110047</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>1110028</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Minion</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1110048</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>1110029</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1110049</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>10009</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Minion</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>1110050</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>1110031</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1110051</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>10010</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Minion</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1110052</v>
       </c>
     </row>
   </sheetData>

--- a/config/data/EnemyTemplate.xlsx
+++ b/config/data/EnemyTemplate.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -655,7 +655,7 @@
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>10012</v>
+        <v>10015</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -668,12 +668,12 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13012</v>
+        <v>13015</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>10013</v>
+        <v>10016</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>13013</v>
+        <v>13016</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>10014</v>
+        <v>10017</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -704,16 +704,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>13014</v>
+        <v>13017</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>10015</v>
+        <v>980002</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -722,16 +722,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>13015</v>
+        <v>980010</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>10016</v>
+        <v>990002</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -740,12 +740,12 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>13016</v>
+        <v>990010</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>10017</v>
+        <v>1000002</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -758,16 +758,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>13017</v>
+        <v>1000010</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>980002</v>
+        <v>1010002</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -776,16 +776,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>980010</v>
+        <v>1010010</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>990002</v>
+        <v>1020002</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -794,16 +794,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>990010</v>
+        <v>1020010</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>1000002</v>
+        <v>1030002</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1000010</v>
+        <v>1030010</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>1010002</v>
+        <v>1040002</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -830,16 +830,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1010010</v>
+        <v>1040010</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>1020002</v>
+        <v>1050002</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -848,12 +848,12 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1020010</v>
+        <v>1050010</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>1030002</v>
+        <v>1060002</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -866,12 +866,12 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1030010</v>
+        <v>1060010</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>1040002</v>
+        <v>1070002</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -884,16 +884,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1040010</v>
+        <v>1070010</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>1050002</v>
+        <v>1080002</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -902,16 +902,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1050010</v>
+        <v>1080010</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>1060002</v>
+        <v>10001</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -920,16 +920,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1060010</v>
+        <v>1090041</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>1070002</v>
+        <v>1090022</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -938,16 +938,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1070010</v>
+        <v>1090042</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>1080002</v>
+        <v>1090023</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -956,12 +956,12 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1080010</v>
+        <v>1090043</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>10001</v>
+        <v>1090024</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -974,16 +974,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1090041</v>
+        <v>1090044</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>1090022</v>
+        <v>1090025</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -992,12 +992,12 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1090042</v>
+        <v>1090045</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>1090023</v>
+        <v>1090026</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1010,16 +1010,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1090043</v>
+        <v>1090046</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>1090024</v>
+        <v>10002</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1028,16 +1028,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1090044</v>
+        <v>1090047</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>1090025</v>
+        <v>1090028</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1046,16 +1046,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1090045</v>
+        <v>1090048</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>1090026</v>
+        <v>1090029</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1064,12 +1064,12 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1090046</v>
+        <v>1090049</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>10002</v>
+        <v>1090030</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1082,12 +1082,12 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1090047</v>
+        <v>1090050</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>1090028</v>
+        <v>1090031</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1100,12 +1100,12 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1090048</v>
+        <v>1090051</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>1090029</v>
+        <v>1090032</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1118,16 +1118,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1090049</v>
+        <v>1090052</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>1090030</v>
+        <v>10003</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1136,16 +1136,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1090050</v>
+        <v>1100041</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>1090031</v>
+        <v>1100022</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1154,12 +1154,12 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1090051</v>
+        <v>1100042</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>1090032</v>
+        <v>1100023</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1172,16 +1172,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1090052</v>
+        <v>1100043</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>10003</v>
+        <v>1100024</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1190,16 +1190,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1100041</v>
+        <v>1100044</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>1100022</v>
+        <v>10005</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1208,12 +1208,12 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1100042</v>
+        <v>1100045</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>1100023</v>
+        <v>1100026</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1226,12 +1226,12 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1100043</v>
+        <v>1100046</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>1100024</v>
+        <v>1100027</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1244,16 +1244,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1100044</v>
+        <v>1100047</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>10005</v>
+        <v>10006</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1262,16 +1262,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1100045</v>
+        <v>1100048</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>1100026</v>
+        <v>1100029</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1280,12 +1280,12 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1100046</v>
+        <v>1100049</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>1100027</v>
+        <v>1100030</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1298,16 +1298,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1100047</v>
+        <v>1100050</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="n">
-        <v>10006</v>
+        <v>1100031</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1316,16 +1316,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1100048</v>
+        <v>1100051</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="n">
-        <v>1100029</v>
+        <v>1100032</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1334,16 +1334,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1100049</v>
+        <v>1100052</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>1100030</v>
+        <v>1110021</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1352,12 +1352,12 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1100050</v>
+        <v>1110041</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>1100031</v>
+        <v>1110022</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1370,16 +1370,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1100051</v>
+        <v>1110042</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="n">
-        <v>1100032</v>
+        <v>1110023</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1388,16 +1388,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1100052</v>
+        <v>1110043</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="n">
-        <v>1110021</v>
+        <v>1110024</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1406,16 +1406,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1110041</v>
+        <v>1110044</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="n">
-        <v>1110022</v>
+        <v>1110025</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1424,16 +1424,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1110042</v>
+        <v>1110045</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" t="n">
-        <v>1110023</v>
+        <v>1110026</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1442,16 +1442,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1110043</v>
+        <v>1110046</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" t="n">
-        <v>1110024</v>
+        <v>10008</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1460,16 +1460,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1110044</v>
+        <v>1110047</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" t="n">
-        <v>1110025</v>
+        <v>1110028</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1478,16 +1478,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1110045</v>
+        <v>1110048</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" t="n">
-        <v>1110026</v>
+        <v>1110029</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1496,16 +1496,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1110046</v>
+        <v>1110049</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" t="n">
-        <v>10008</v>
+        <v>10009</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1514,16 +1514,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1110047</v>
+        <v>1110050</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" t="n">
-        <v>1110028</v>
+        <v>1110031</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1110048</v>
+        <v>1110051</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="n">
-        <v>1110029</v>
+        <v>10010</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1550,16 +1550,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1110049</v>
+        <v>1110052</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="n">
-        <v>10009</v>
+        <v>1120021</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1110050</v>
+        <v>1120041</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" t="n">
-        <v>1110031</v>
+        <v>1120022</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1586,25 +1586,187 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1110051</v>
+        <v>1120042</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" t="n">
-        <v>10010</v>
+        <v>1120023</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1120043</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>1120024</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>1120044</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>10012</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>1120045</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>1120026</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>1120046</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>1120027</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>1120047</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>10013</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>1120048</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>10014</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1120049</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>1120030</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
           <t>Minion</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>1110052</v>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1120050</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>1120031</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Minion</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1120051</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>1120032</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>1120052</v>
       </c>
     </row>
   </sheetData>

--- a/config/data/EnemyTemplate.xlsx
+++ b/config/data/EnemyTemplate.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1769,6 +1769,222 @@
         <v>1120052</v>
       </c>
     </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>1130021</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>1130041</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>1130022</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>1130042</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>1130023</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>1130043</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>1130024</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>1130044</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>1130025</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>1130045</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>1130026</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>1130046</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>1130027</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>1130047</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>1130028</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>1130048</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>1130029</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1130049</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>1130030</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>1130050</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>1130031</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>1130051</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>1130032</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>1130052</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyTemplate.xlsx
+++ b/config/data/EnemyTemplate.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -673,11 +673,11 @@
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>10016</v>
+        <v>10017</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>13016</v>
+        <v>13017</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>10017</v>
+        <v>980002</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -704,16 +704,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>13017</v>
+        <v>980010</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>980002</v>
+        <v>990002</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -722,12 +722,12 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>980010</v>
+        <v>990010</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>990002</v>
+        <v>1000002</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -740,12 +740,12 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>990010</v>
+        <v>1000010</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>1000002</v>
+        <v>1010002</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -758,16 +758,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1000010</v>
+        <v>1010010</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>1010002</v>
+        <v>1020002</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -776,12 +776,12 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1010010</v>
+        <v>1020010</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>1020002</v>
+        <v>1030002</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -794,12 +794,12 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1020010</v>
+        <v>1030010</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>1030002</v>
+        <v>1040002</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1030010</v>
+        <v>1040010</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>1040002</v>
+        <v>1050002</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -830,16 +830,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1040010</v>
+        <v>1050010</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>1050002</v>
+        <v>1060002</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -848,12 +848,12 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1050010</v>
+        <v>1060010</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>1060002</v>
+        <v>1070002</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -866,12 +866,12 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1060010</v>
+        <v>1070010</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>1070002</v>
+        <v>1080002</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -884,16 +884,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1070010</v>
+        <v>1080010</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>1080002</v>
+        <v>10001</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -902,16 +902,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1080010</v>
+        <v>1090041</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>10001</v>
+        <v>1090022</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -920,12 +920,12 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1090041</v>
+        <v>1090042</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>1090022</v>
+        <v>1090023</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -938,16 +938,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1090042</v>
+        <v>1090043</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>1090023</v>
+        <v>1090024</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -956,16 +956,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1090043</v>
+        <v>1090044</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>1090024</v>
+        <v>1090025</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -974,16 +974,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1090044</v>
+        <v>1090045</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>1090025</v>
+        <v>1090026</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -992,12 +992,12 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1090045</v>
+        <v>1090046</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>1090026</v>
+        <v>10002</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1010,12 +1010,12 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1090046</v>
+        <v>1090047</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>10002</v>
+        <v>1090028</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1028,16 +1028,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1090047</v>
+        <v>1090048</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>1090028</v>
+        <v>1090029</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1046,16 +1046,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1090048</v>
+        <v>1090049</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>1090029</v>
+        <v>1090030</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1064,12 +1064,12 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1090049</v>
+        <v>1090050</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>1090030</v>
+        <v>1090031</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1090050</v>
+        <v>1090051</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>1090031</v>
+        <v>1090032</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1100,12 +1100,12 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1090051</v>
+        <v>1090052</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>1090032</v>
+        <v>10003</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1118,16 +1118,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1090052</v>
+        <v>1100041</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>10003</v>
+        <v>1100022</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1136,16 +1136,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1100041</v>
+        <v>1100042</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>1100022</v>
+        <v>1100023</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1154,16 +1154,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1100042</v>
+        <v>1100043</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>1100023</v>
+        <v>1100024</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1172,16 +1172,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1100043</v>
+        <v>1100044</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>1100024</v>
+        <v>10005</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1190,12 +1190,12 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1100044</v>
+        <v>1100045</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>10005</v>
+        <v>1100026</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1208,16 +1208,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1100045</v>
+        <v>1100046</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>1100026</v>
+        <v>1100027</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1226,12 +1226,12 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1100046</v>
+        <v>1100047</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>1100027</v>
+        <v>10006</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1244,12 +1244,12 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1100047</v>
+        <v>1100048</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>10006</v>
+        <v>1100029</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1262,12 +1262,12 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1100048</v>
+        <v>1100049</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>1100029</v>
+        <v>1100030</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1100049</v>
+        <v>1100050</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>1100030</v>
+        <v>1100031</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1298,16 +1298,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1100050</v>
+        <v>1100051</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="n">
-        <v>1100031</v>
+        <v>1100032</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1316,12 +1316,12 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1100051</v>
+        <v>1100052</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="n">
-        <v>1100032</v>
+        <v>1110021</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1334,16 +1334,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1100052</v>
+        <v>1110041</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>1110021</v>
+        <v>1110022</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1352,16 +1352,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1110041</v>
+        <v>1110042</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>1110022</v>
+        <v>1110023</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1370,12 +1370,12 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1110042</v>
+        <v>1110043</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="n">
-        <v>1110023</v>
+        <v>1110024</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1388,16 +1388,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1110043</v>
+        <v>1110044</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="n">
-        <v>1110024</v>
+        <v>1110025</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1406,16 +1406,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1110044</v>
+        <v>1110045</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="n">
-        <v>1110025</v>
+        <v>1110026</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1424,16 +1424,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1110045</v>
+        <v>1110046</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" t="n">
-        <v>1110026</v>
+        <v>10008</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1442,16 +1442,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1110046</v>
+        <v>1110047</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" t="n">
-        <v>10008</v>
+        <v>1110028</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1460,16 +1460,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1110047</v>
+        <v>1110048</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" t="n">
-        <v>1110028</v>
+        <v>1110029</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1478,16 +1478,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1110048</v>
+        <v>1110049</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" t="n">
-        <v>1110029</v>
+        <v>10009</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1496,16 +1496,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1110049</v>
+        <v>1110050</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" t="n">
-        <v>10009</v>
+        <v>1110031</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1514,16 +1514,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1110050</v>
+        <v>1110051</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" t="n">
-        <v>1110031</v>
+        <v>10010</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1110051</v>
+        <v>1110052</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="n">
-        <v>10010</v>
+        <v>1120021</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1550,12 +1550,12 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1110052</v>
+        <v>1120041</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="n">
-        <v>1120021</v>
+        <v>1120022</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1120041</v>
+        <v>1120042</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" t="n">
-        <v>1120022</v>
+        <v>1120023</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1586,16 +1586,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1120042</v>
+        <v>1120043</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" t="n">
-        <v>1120023</v>
+        <v>1120024</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1604,12 +1604,12 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1120043</v>
+        <v>1120044</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" t="n">
-        <v>1120024</v>
+        <v>10012</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1622,12 +1622,12 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1120044</v>
+        <v>1120045</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" t="n">
-        <v>10012</v>
+        <v>1120026</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1640,12 +1640,12 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1120045</v>
+        <v>1120046</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" t="n">
-        <v>1120026</v>
+        <v>1120027</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1658,12 +1658,12 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1120046</v>
+        <v>1120047</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" t="n">
-        <v>1120027</v>
+        <v>10013</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1676,12 +1676,12 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1120047</v>
+        <v>1120048</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" t="n">
-        <v>10013</v>
+        <v>10014</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1694,16 +1694,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1120048</v>
+        <v>1120049</v>
       </c>
     </row>
     <row r="69">
       <c r="B69" t="n">
-        <v>10014</v>
+        <v>1120030</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -1712,12 +1712,12 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1120049</v>
+        <v>1120050</v>
       </c>
     </row>
     <row r="70">
       <c r="B70" t="n">
-        <v>1120030</v>
+        <v>1120031</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -1730,16 +1730,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1120050</v>
+        <v>1120051</v>
       </c>
     </row>
     <row r="71">
       <c r="B71" t="n">
-        <v>1120031</v>
+        <v>1120032</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1748,16 +1748,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1120051</v>
+        <v>1120052</v>
       </c>
     </row>
     <row r="72">
       <c r="B72" t="n">
-        <v>1120032</v>
+        <v>1130021</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -1766,16 +1766,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1120052</v>
+        <v>1130041</v>
       </c>
     </row>
     <row r="73">
       <c r="B73" t="n">
-        <v>1130021</v>
+        <v>1130022</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -1784,16 +1784,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1130041</v>
+        <v>1130042</v>
       </c>
     </row>
     <row r="74">
       <c r="B74" t="n">
-        <v>1130022</v>
+        <v>1130023</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -1802,12 +1802,12 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1130042</v>
+        <v>1130043</v>
       </c>
     </row>
     <row r="75">
       <c r="B75" t="n">
-        <v>1130023</v>
+        <v>1130024</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1820,12 +1820,12 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1130043</v>
+        <v>1130044</v>
       </c>
     </row>
     <row r="76">
       <c r="B76" t="n">
-        <v>1130024</v>
+        <v>1130025</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1838,16 +1838,16 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1130044</v>
+        <v>1130045</v>
       </c>
     </row>
     <row r="77">
       <c r="B77" t="n">
-        <v>1130025</v>
+        <v>1130026</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -1856,12 +1856,12 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1130045</v>
+        <v>1130046</v>
       </c>
     </row>
     <row r="78">
       <c r="B78" t="n">
-        <v>1130026</v>
+        <v>1130027</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -1874,16 +1874,16 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1130046</v>
+        <v>1130047</v>
       </c>
     </row>
     <row r="79">
       <c r="B79" t="n">
-        <v>1130027</v>
+        <v>1130028</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -1892,16 +1892,16 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1130047</v>
+        <v>1130048</v>
       </c>
     </row>
     <row r="80">
       <c r="B80" t="n">
-        <v>1130028</v>
+        <v>1130029</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -1910,16 +1910,16 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1130048</v>
+        <v>1130049</v>
       </c>
     </row>
     <row r="81">
       <c r="B81" t="n">
-        <v>1130029</v>
+        <v>1130030</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -1928,12 +1928,12 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1130049</v>
+        <v>1130050</v>
       </c>
     </row>
     <row r="82">
       <c r="B82" t="n">
-        <v>1130030</v>
+        <v>1130031</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -1946,12 +1946,12 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1130050</v>
+        <v>1130051</v>
       </c>
     </row>
     <row r="83">
       <c r="B83" t="n">
-        <v>1130031</v>
+        <v>1130032</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -1964,16 +1964,16 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1130051</v>
+        <v>1130052</v>
       </c>
     </row>
     <row r="84">
       <c r="B84" t="n">
-        <v>1130032</v>
+        <v>1140021</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -1982,7 +1982,205 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1130052</v>
+        <v>1140041</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>1140022</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>1140042</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>1140023</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>1140043</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>1140024</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>1140044</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="n">
+        <v>1140025</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>1140045</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="n">
+        <v>1140026</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>1140046</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="n">
+        <v>1140027</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>1140047</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="n">
+        <v>1140028</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>1140048</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="n">
+        <v>1140029</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>1140049</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="n">
+        <v>1140030</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>1140050</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="n">
+        <v>10016</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>1140051</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="n">
+        <v>1140032</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>1140052</v>
       </c>
     </row>
   </sheetData>

--- a/config/data/EnemyTemplate.xlsx
+++ b/config/data/EnemyTemplate.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J95"/>
+  <dimension ref="A1:J97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -673,11 +673,11 @@
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>10017</v>
+        <v>980002</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>13017</v>
+        <v>980010</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>980002</v>
+        <v>990002</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -704,12 +704,12 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>980010</v>
+        <v>990010</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>990002</v>
+        <v>1000002</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -722,12 +722,12 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>990010</v>
+        <v>1000010</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>1000002</v>
+        <v>1010002</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -740,16 +740,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1000010</v>
+        <v>1010010</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>1010002</v>
+        <v>1020002</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -758,12 +758,12 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1010010</v>
+        <v>1020010</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>1020002</v>
+        <v>1030002</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -776,12 +776,12 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1020010</v>
+        <v>1030010</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>1030002</v>
+        <v>1040002</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -794,16 +794,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1030010</v>
+        <v>1040010</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>1040002</v>
+        <v>1050002</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1040010</v>
+        <v>1050010</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>1050002</v>
+        <v>1060002</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -830,12 +830,12 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1050010</v>
+        <v>1060010</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>1060002</v>
+        <v>1070002</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -848,12 +848,12 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1060010</v>
+        <v>1070010</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>1070002</v>
+        <v>1080002</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -866,16 +866,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1070010</v>
+        <v>1080010</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>1080002</v>
+        <v>10001</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -884,16 +884,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1080010</v>
+        <v>1090041</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>10001</v>
+        <v>1090022</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -902,12 +902,12 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1090041</v>
+        <v>1090042</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>1090022</v>
+        <v>1090023</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -920,16 +920,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1090042</v>
+        <v>1090043</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>1090023</v>
+        <v>1090024</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -938,16 +938,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1090043</v>
+        <v>1090044</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>1090024</v>
+        <v>1090025</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -956,16 +956,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1090044</v>
+        <v>1090045</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>1090025</v>
+        <v>1090026</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -974,12 +974,12 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1090045</v>
+        <v>1090046</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>1090026</v>
+        <v>10002</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -992,12 +992,12 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1090046</v>
+        <v>1090047</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>10002</v>
+        <v>1090028</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1010,16 +1010,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1090047</v>
+        <v>1090048</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>1090028</v>
+        <v>1090029</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1028,16 +1028,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1090048</v>
+        <v>1090049</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>1090029</v>
+        <v>1090030</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1046,12 +1046,12 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1090049</v>
+        <v>1090050</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>1090030</v>
+        <v>1090031</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1064,16 +1064,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1090050</v>
+        <v>1090051</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>1090031</v>
+        <v>1090032</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1082,12 +1082,12 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1090051</v>
+        <v>1090052</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>1090032</v>
+        <v>10003</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1100,16 +1100,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1090052</v>
+        <v>1100041</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>10003</v>
+        <v>1100022</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1118,16 +1118,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1100041</v>
+        <v>1100042</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>1100022</v>
+        <v>1100023</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1136,16 +1136,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1100042</v>
+        <v>1100043</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>1100023</v>
+        <v>1100024</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1154,16 +1154,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1100043</v>
+        <v>1100044</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>1100024</v>
+        <v>10005</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1172,12 +1172,12 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1100044</v>
+        <v>1100045</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>10005</v>
+        <v>1100026</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1190,16 +1190,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1100045</v>
+        <v>1100046</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>1100026</v>
+        <v>1100027</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1208,12 +1208,12 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1100046</v>
+        <v>1100047</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>1100027</v>
+        <v>10006</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1226,12 +1226,12 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1100047</v>
+        <v>1100048</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>10006</v>
+        <v>1100029</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1244,12 +1244,12 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1100048</v>
+        <v>1100049</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>1100029</v>
+        <v>1100030</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1262,16 +1262,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1100049</v>
+        <v>1100050</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>1100030</v>
+        <v>1100031</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1280,16 +1280,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1100050</v>
+        <v>1100051</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>1100031</v>
+        <v>1100032</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1298,12 +1298,12 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1100051</v>
+        <v>1100052</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="n">
-        <v>1100032</v>
+        <v>1110021</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1316,16 +1316,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1100052</v>
+        <v>1110041</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="n">
-        <v>1110021</v>
+        <v>1110022</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1334,16 +1334,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1110041</v>
+        <v>1110042</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>1110022</v>
+        <v>1110023</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1352,12 +1352,12 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1110042</v>
+        <v>1110043</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>1110023</v>
+        <v>1110024</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1370,16 +1370,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1110043</v>
+        <v>1110044</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="n">
-        <v>1110024</v>
+        <v>1110025</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1388,16 +1388,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1110044</v>
+        <v>1110045</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="n">
-        <v>1110025</v>
+        <v>1110026</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1406,16 +1406,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1110045</v>
+        <v>1110046</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="n">
-        <v>1110026</v>
+        <v>10008</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1424,16 +1424,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1110046</v>
+        <v>1110047</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" t="n">
-        <v>10008</v>
+        <v>1110028</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1442,16 +1442,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1110047</v>
+        <v>1110048</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" t="n">
-        <v>1110028</v>
+        <v>1110029</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1460,16 +1460,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1110048</v>
+        <v>1110049</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" t="n">
-        <v>1110029</v>
+        <v>10009</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1478,16 +1478,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1110049</v>
+        <v>1110050</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" t="n">
-        <v>10009</v>
+        <v>1110031</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1496,16 +1496,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1110050</v>
+        <v>1110051</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" t="n">
-        <v>1110031</v>
+        <v>10010</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1514,16 +1514,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1110051</v>
+        <v>1110052</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" t="n">
-        <v>10010</v>
+        <v>1120021</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1532,12 +1532,12 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1110052</v>
+        <v>1120041</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="n">
-        <v>1120021</v>
+        <v>1120022</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1550,16 +1550,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1120041</v>
+        <v>1120042</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="n">
-        <v>1120022</v>
+        <v>1120023</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1120042</v>
+        <v>1120043</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" t="n">
-        <v>1120023</v>
+        <v>1120024</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1586,12 +1586,12 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1120043</v>
+        <v>1120044</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" t="n">
-        <v>1120024</v>
+        <v>10012</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1604,12 +1604,12 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1120044</v>
+        <v>1120045</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" t="n">
-        <v>10012</v>
+        <v>1120026</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1622,12 +1622,12 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1120045</v>
+        <v>1120046</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" t="n">
-        <v>1120026</v>
+        <v>1120027</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1640,12 +1640,12 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1120046</v>
+        <v>1120047</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" t="n">
-        <v>1120027</v>
+        <v>10013</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1658,12 +1658,12 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1120047</v>
+        <v>1120048</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" t="n">
-        <v>10013</v>
+        <v>10014</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1676,16 +1676,16 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1120048</v>
+        <v>1120049</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" t="n">
-        <v>10014</v>
+        <v>1120030</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -1694,12 +1694,12 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1120049</v>
+        <v>1120050</v>
       </c>
     </row>
     <row r="69">
       <c r="B69" t="n">
-        <v>1120030</v>
+        <v>1120031</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1120050</v>
+        <v>1120051</v>
       </c>
     </row>
     <row r="70">
       <c r="B70" t="n">
-        <v>1120031</v>
+        <v>1120032</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -1730,16 +1730,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1120051</v>
+        <v>1120052</v>
       </c>
     </row>
     <row r="71">
       <c r="B71" t="n">
-        <v>1120032</v>
+        <v>1130021</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1748,16 +1748,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1120052</v>
+        <v>1130041</v>
       </c>
     </row>
     <row r="72">
       <c r="B72" t="n">
-        <v>1130021</v>
+        <v>1130022</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -1766,16 +1766,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1130041</v>
+        <v>1130042</v>
       </c>
     </row>
     <row r="73">
       <c r="B73" t="n">
-        <v>1130022</v>
+        <v>1130023</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -1784,12 +1784,12 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1130042</v>
+        <v>1130043</v>
       </c>
     </row>
     <row r="74">
       <c r="B74" t="n">
-        <v>1130023</v>
+        <v>1130024</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1802,12 +1802,12 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1130043</v>
+        <v>1130044</v>
       </c>
     </row>
     <row r="75">
       <c r="B75" t="n">
-        <v>1130024</v>
+        <v>1130025</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1820,16 +1820,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1130044</v>
+        <v>1130045</v>
       </c>
     </row>
     <row r="76">
       <c r="B76" t="n">
-        <v>1130025</v>
+        <v>1130026</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -1838,12 +1838,12 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1130045</v>
+        <v>1130046</v>
       </c>
     </row>
     <row r="77">
       <c r="B77" t="n">
-        <v>1130026</v>
+        <v>1130027</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1856,16 +1856,16 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1130046</v>
+        <v>1130047</v>
       </c>
     </row>
     <row r="78">
       <c r="B78" t="n">
-        <v>1130027</v>
+        <v>1130028</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -1874,16 +1874,16 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1130047</v>
+        <v>1130048</v>
       </c>
     </row>
     <row r="79">
       <c r="B79" t="n">
-        <v>1130028</v>
+        <v>1130029</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -1892,16 +1892,16 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1130048</v>
+        <v>1130049</v>
       </c>
     </row>
     <row r="80">
       <c r="B80" t="n">
-        <v>1130029</v>
+        <v>1130030</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -1910,12 +1910,12 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1130049</v>
+        <v>1130050</v>
       </c>
     </row>
     <row r="81">
       <c r="B81" t="n">
-        <v>1130030</v>
+        <v>1130031</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -1928,12 +1928,12 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1130050</v>
+        <v>1130051</v>
       </c>
     </row>
     <row r="82">
       <c r="B82" t="n">
-        <v>1130031</v>
+        <v>1130032</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -1946,16 +1946,16 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1130051</v>
+        <v>1130052</v>
       </c>
     </row>
     <row r="83">
       <c r="B83" t="n">
-        <v>1130032</v>
+        <v>1140021</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -1964,16 +1964,16 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1130052</v>
+        <v>1140041</v>
       </c>
     </row>
     <row r="84">
       <c r="B84" t="n">
-        <v>1140021</v>
+        <v>1140022</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -1982,12 +1982,12 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1140041</v>
+        <v>1140042</v>
       </c>
     </row>
     <row r="85">
       <c r="B85" t="n">
-        <v>1140022</v>
+        <v>1140023</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -2000,12 +2000,12 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1140042</v>
+        <v>1140043</v>
       </c>
     </row>
     <row r="86">
       <c r="B86" t="n">
-        <v>1140023</v>
+        <v>1140024</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -2018,12 +2018,12 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1140043</v>
+        <v>1140044</v>
       </c>
     </row>
     <row r="87">
       <c r="B87" t="n">
-        <v>1140024</v>
+        <v>1140025</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -2036,12 +2036,12 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1140044</v>
+        <v>1140045</v>
       </c>
     </row>
     <row r="88">
       <c r="B88" t="n">
-        <v>1140025</v>
+        <v>1140026</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -2054,12 +2054,12 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1140045</v>
+        <v>1140046</v>
       </c>
     </row>
     <row r="89">
       <c r="B89" t="n">
-        <v>1140026</v>
+        <v>1140027</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -2072,12 +2072,12 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1140046</v>
+        <v>1140047</v>
       </c>
     </row>
     <row r="90">
       <c r="B90" t="n">
-        <v>1140027</v>
+        <v>1140028</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -2090,12 +2090,12 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1140047</v>
+        <v>1140048</v>
       </c>
     </row>
     <row r="91">
       <c r="B91" t="n">
-        <v>1140028</v>
+        <v>1140029</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -2108,12 +2108,12 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1140048</v>
+        <v>1140049</v>
       </c>
     </row>
     <row r="92">
       <c r="B92" t="n">
-        <v>1140029</v>
+        <v>1140030</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -2126,12 +2126,12 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1140049</v>
+        <v>1140050</v>
       </c>
     </row>
     <row r="93">
       <c r="B93" t="n">
-        <v>1140030</v>
+        <v>10016</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -2144,16 +2144,16 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1140050</v>
+        <v>1140051</v>
       </c>
     </row>
     <row r="94">
       <c r="B94" t="n">
-        <v>10016</v>
+        <v>1140032</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2162,12 +2162,12 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1140051</v>
+        <v>1140052</v>
       </c>
     </row>
     <row r="95">
       <c r="B95" t="n">
-        <v>1140032</v>
+        <v>10017</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -2180,7 +2180,43 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1140052</v>
+        <v>1150041</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="n">
+        <v>1150022</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Minion</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>1150042</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="n">
+        <v>1150023</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>1150043</v>
       </c>
     </row>
   </sheetData>

--- a/config/data/EnemyTemplate.xlsx
+++ b/config/data/EnemyTemplate.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,11 +601,11 @@
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>10001</v>
+        <v>10004</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>13001</v>
+        <v>13004</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>10002</v>
+        <v>10007</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -632,16 +632,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>13002</v>
+        <v>13007</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>10003</v>
+        <v>10011</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -650,16 +650,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>13003</v>
+        <v>13011</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>10004</v>
+        <v>10015</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -668,16 +668,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13004</v>
+        <v>13015</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>10005</v>
+        <v>980002</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -686,12 +686,12 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>13005</v>
+        <v>980010</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>10006</v>
+        <v>990002</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>13006</v>
+        <v>990010</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>10007</v>
+        <v>1000002</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -722,16 +722,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>13007</v>
+        <v>1000010</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>10008</v>
+        <v>1010002</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -740,16 +740,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>13008</v>
+        <v>1010010</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>10009</v>
+        <v>1020002</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -758,16 +758,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>13009</v>
+        <v>1020010</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>10010</v>
+        <v>1030002</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -776,12 +776,12 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>13010</v>
+        <v>1030010</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>10011</v>
+        <v>1040002</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -794,16 +794,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>13011</v>
+        <v>1040010</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>10012</v>
+        <v>1050002</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>13012</v>
+        <v>1050010</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>10013</v>
+        <v>1060002</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -830,16 +830,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>13013</v>
+        <v>1060010</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>10014</v>
+        <v>1070002</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -848,16 +848,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>13014</v>
+        <v>1070010</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>10015</v>
+        <v>1080002</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -866,12 +866,12 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>13015</v>
+        <v>1080010</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>10016</v>
+        <v>10001</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -884,25 +884,1339 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>13016</v>
+        <v>1090041</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
+        <v>1090022</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1090042</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>1090023</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1090043</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>1090024</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1090044</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>1090025</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Minion</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1090045</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>1090026</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1090046</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>10002</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1090047</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>1090028</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1090048</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>1090029</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1090049</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>1090030</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1090050</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>1090031</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1090051</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>1090032</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1090052</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>10003</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1100041</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>1100022</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Minion</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1100042</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>1100023</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1100043</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>1100024</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1100044</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>10005</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1100045</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>1100026</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1100046</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>1100027</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1100047</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>10006</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1100048</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>1100029</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1100049</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>1100030</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1100050</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>1100031</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Minion</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1100051</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>1100032</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1100052</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>1110021</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1110041</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>1110022</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Minion</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1110042</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>1110023</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1110043</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>1110024</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1110044</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>1110025</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1110045</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>1110026</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Minion</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1110046</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>10008</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1110047</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>1110028</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Minion</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1110048</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>1110029</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1110049</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>10009</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Minion</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1110050</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>1110031</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1110051</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>10010</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Minion</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>1110052</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>1120021</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1120041</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>1120022</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1120042</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>1120023</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>1120043</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>1120024</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1120044</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>10012</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1120045</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>1120026</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>1120046</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>1120027</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>1120047</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>10013</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>1120048</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>10014</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>1120049</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>1120030</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Minion</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>1120050</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>1120031</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Minion</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1120051</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>1120032</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1120052</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>1130021</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1130041</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>1130022</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>1130042</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>1130023</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>1130043</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>1130024</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>1130044</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>1130025</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>1130045</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>1130026</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>1130046</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>1130027</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>1130047</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>1130028</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>1130048</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>1130029</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>1130049</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>1130030</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>1130050</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>1130031</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1130051</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>1130032</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>1130052</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>1140021</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Minion</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>1140041</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>1140022</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>1140042</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>1140023</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>1140043</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>1140024</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>1140044</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>1140025</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>1140045</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="n">
+        <v>1140026</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>1140046</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="n">
+        <v>1140027</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>1140047</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="n">
+        <v>1140028</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>1140048</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="n">
+        <v>1140029</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>1140049</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="n">
+        <v>1140030</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>1140050</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="n">
+        <v>10016</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>1140051</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="n">
+        <v>1140032</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>1140052</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="n">
         <v>10017</v>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Elite</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>13017</v>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>1150041</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="n">
+        <v>1150022</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Minion</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>1150042</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="n">
+        <v>1150023</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>1150043</v>
       </c>
     </row>
   </sheetData>

--- a/config/data/EnemyTemplate.xlsx
+++ b/config/data/EnemyTemplate.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="EnemyTemplate" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyTemplate" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -24,16 +24,68 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF1F2937"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F3A4A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9EEF5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3D6E8F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE5EF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8FB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -41,12 +93,45 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -414,194 +499,209 @@
   </sheetPr>
   <dimension ref="A1:J97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12.7109375" customWidth="1" min="1" max="1"/>
+    <col width="23.7109375" customWidth="1" style="5" min="2" max="2"/>
+    <col width="15.7109375" customWidth="1" style="5" min="3" max="3"/>
+    <col width="18.7109375" customWidth="1" style="5" min="4" max="4"/>
+    <col width="19.7109375" customWidth="1" style="5" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>@table</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>EnemyTemplate</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>@mode</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>@key</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>@scope</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>@schema</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>1a5340995b67d6bd</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>7faeb816621a164f</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>#name</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>base_aggro_decimal</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>default_ai_graph_id</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>#field</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>base_aggro_decimal</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>default_ai_graph_id</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>#type</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>ref&lt;ContentIdentity.id&gt;</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>enum&lt;EnemyRank&gt;</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>ref&lt;AiGraph.id&gt;</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>#scope</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>all</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>#input</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>length=1..32</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="E6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>#desc</t>
         </is>
       </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" t="n">
-        <v>10004</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>10004</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -613,13 +713,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>13004</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>13004</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="n">
-        <v>10007</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>10007</t>
+        </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -631,13 +735,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>13007</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>13007</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="n">
-        <v>10011</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>10011</t>
+        </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -649,13 +757,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>13011</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>13011</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="n">
-        <v>10015</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>10015</t>
+        </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -667,13 +779,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>13015</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>13015</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="n">
-        <v>980002</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>980002</t>
+        </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -685,13 +801,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>980010</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>980010</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="n">
-        <v>990002</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>990002</t>
+        </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -703,13 +823,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>990010</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>990010</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="n">
-        <v>1000002</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1000002</t>
+        </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -721,13 +845,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>1000010</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1000010</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="n">
-        <v>1010002</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1010002</t>
+        </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -739,13 +867,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="E15" t="n">
-        <v>1010010</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1010010</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="n">
-        <v>1020002</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1040002</t>
+        </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -757,67 +889,83 @@
           <t>100</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>1020010</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1040010</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="n">
-        <v>1030002</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1050002</t>
+        </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1050010</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1060002</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>Boss</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>1030010</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="n">
-        <v>1040002</v>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1060010</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1070002</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Boss</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>1040010</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="n">
-        <v>1050002</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Elite</t>
-        </is>
-      </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v>1050010</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1070010</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="n">
-        <v>1060002</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1080002</t>
+        </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -829,17 +977,21 @@
           <t>100</t>
         </is>
       </c>
-      <c r="E20" t="n">
-        <v>1060010</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1080010</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="n">
-        <v>1070002</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>10001</t>
+        </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -847,17 +999,21 @@
           <t>100</t>
         </is>
       </c>
-      <c r="E21" t="n">
-        <v>1070010</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1090041</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="n">
-        <v>1080002</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1090022</t>
+        </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -865,17 +1021,21 @@
           <t>100</t>
         </is>
       </c>
-      <c r="E22" t="n">
-        <v>1080010</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1090042</t>
+        </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="n">
-        <v>10001</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1090023</t>
+        </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -883,17 +1043,21 @@
           <t>100</t>
         </is>
       </c>
-      <c r="E23" t="n">
-        <v>1090041</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1090043</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="n">
-        <v>1090022</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1090024</t>
+        </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -901,17 +1065,21 @@
           <t>100</t>
         </is>
       </c>
-      <c r="E24" t="n">
-        <v>1090042</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1090044</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="n">
-        <v>1090023</v>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1090025</t>
+        </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -919,17 +1087,21 @@
           <t>100</t>
         </is>
       </c>
-      <c r="E25" t="n">
-        <v>1090043</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1090045</t>
+        </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="n">
-        <v>1090024</v>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1090026</t>
+        </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -937,157 +1109,193 @@
           <t>100</t>
         </is>
       </c>
-      <c r="E26" t="n">
-        <v>1090044</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1090046</t>
+        </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="n">
-        <v>1090025</v>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>10002</t>
+        </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1090047</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1090028</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1090048</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1090029</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1090049</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1090030</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1090050</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1090031</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1090051</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1090032</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1090052</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>10003</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1100041</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1100022</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
           <t>Minion</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>1090045</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" t="n">
-        <v>1090026</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Elite</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>1090046</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" t="n">
-        <v>10002</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Elite</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>1090047</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" t="n">
-        <v>1090028</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Elite</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>1090048</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="n">
-        <v>1090029</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>1090049</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" t="n">
-        <v>1090030</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Elite</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>1090050</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" t="n">
-        <v>1090031</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Elite</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>1090051</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" t="n">
-        <v>1090032</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
       <c r="D34" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E34" t="n">
-        <v>1090052</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1100042</t>
+        </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="n">
-        <v>10003</v>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1100023</t>
+        </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1099,161 +1307,197 @@
           <t>100</t>
         </is>
       </c>
-      <c r="E35" t="n">
-        <v>1100041</v>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1100043</t>
+        </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="n">
-        <v>1100022</v>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1100024</t>
+        </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1100044</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>10005</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1100045</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1100026</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1100046</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1100027</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1100047</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>10006</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1100048</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1100029</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1100049</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1100030</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1100050</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1100031</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>Minion</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>1100042</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" t="n">
-        <v>1100023</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>1100043</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" t="n">
-        <v>1100024</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Elite</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>1100044</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" t="n">
-        <v>10005</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>1100045</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" t="n">
-        <v>1100026</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>1100046</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" t="n">
-        <v>1100027</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Elite</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>1100047</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" t="n">
-        <v>10006</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Elite</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>1100048</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" t="n">
-        <v>1100029</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Elite</t>
-        </is>
-      </c>
       <c r="D43" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E43" t="n">
-        <v>1100049</v>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1100051</t>
+        </is>
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="n">
-        <v>1100030</v>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1100032</t>
+        </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1261,53 +1505,65 @@
           <t>100</t>
         </is>
       </c>
-      <c r="E44" t="n">
-        <v>1100050</v>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1100052</t>
+        </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" t="n">
-        <v>1100031</v>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1110021</t>
+        </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1110041</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1110022</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
           <t>Minion</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>1100051</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" t="n">
-        <v>1100032</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
       <c r="D46" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E46" t="n">
-        <v>1100052</v>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1110042</t>
+        </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" t="n">
-        <v>1110021</v>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1110023</t>
+        </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1315,67 +1571,83 @@
           <t>100</t>
         </is>
       </c>
-      <c r="E47" t="n">
-        <v>1110041</v>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1110043</t>
+        </is>
       </c>
     </row>
     <row r="48">
-      <c r="B48" t="n">
-        <v>1110022</v>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1110024</t>
+        </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1110044</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1110025</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1110045</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1110026</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
           <t>Minion</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>1110042</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" t="n">
-        <v>1110023</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Elite</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>1110043</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" t="n">
-        <v>1110024</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Elite</t>
-        </is>
-      </c>
       <c r="D50" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E50" t="n">
-        <v>1110044</v>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1110046</t>
+        </is>
       </c>
     </row>
     <row r="51">
-      <c r="B51" t="n">
-        <v>1110025</v>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>10008</t>
+        </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1387,13 +1659,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="E51" t="n">
-        <v>1110045</v>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1110047</t>
+        </is>
       </c>
     </row>
     <row r="52">
-      <c r="B52" t="n">
-        <v>1110026</v>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1110028</t>
+        </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1405,13 +1681,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="E52" t="n">
-        <v>1110046</v>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1110048</t>
+        </is>
       </c>
     </row>
     <row r="53">
-      <c r="B53" t="n">
-        <v>10008</v>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1110029</t>
+        </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1423,13 +1703,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="E53" t="n">
-        <v>1110047</v>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1110049</t>
+        </is>
       </c>
     </row>
     <row r="54">
-      <c r="B54" t="n">
-        <v>1110028</v>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>10009</t>
+        </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1441,17 +1725,21 @@
           <t>100</t>
         </is>
       </c>
-      <c r="E54" t="n">
-        <v>1110048</v>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1110050</t>
+        </is>
       </c>
     </row>
     <row r="55">
-      <c r="B55" t="n">
-        <v>1110029</v>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1110031</t>
+        </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1459,13 +1747,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="E55" t="n">
-        <v>1110049</v>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1110051</t>
+        </is>
       </c>
     </row>
     <row r="56">
-      <c r="B56" t="n">
-        <v>10009</v>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>10010</t>
+        </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1477,17 +1769,21 @@
           <t>100</t>
         </is>
       </c>
-      <c r="E56" t="n">
-        <v>1110050</v>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1110052</t>
+        </is>
       </c>
     </row>
     <row r="57">
-      <c r="B57" t="n">
-        <v>1110031</v>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1120021</t>
+        </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1495,179 +1791,219 @@
           <t>100</t>
         </is>
       </c>
-      <c r="E57" t="n">
-        <v>1110051</v>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1120041</t>
+        </is>
       </c>
     </row>
     <row r="58">
-      <c r="B58" t="n">
-        <v>10010</v>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1120022</t>
+        </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1120042</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1120023</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>1120043</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1120024</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1120044</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>10012</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1120045</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1120026</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1120046</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1120027</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1120047</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>10013</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1120048</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>10014</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1120049</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1120030</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
           <t>Minion</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>1110052</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" t="n">
-        <v>1120021</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>1120041</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" t="n">
-        <v>1120022</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>1120042</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="B61" t="n">
-        <v>1120023</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Elite</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>1120043</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" t="n">
-        <v>1120024</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>1120044</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" t="n">
-        <v>10012</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>1120045</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="B64" t="n">
-        <v>1120026</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>1120046</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" t="n">
-        <v>1120027</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>1120047</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" t="n">
-        <v>10013</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
       <c r="D66" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E66" t="n">
-        <v>1120048</v>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>1120050</t>
+        </is>
       </c>
     </row>
     <row r="67">
-      <c r="B67" t="n">
-        <v>10014</v>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1120031</t>
+        </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1675,287 +2011,351 @@
           <t>100</t>
         </is>
       </c>
-      <c r="E67" t="n">
-        <v>1120049</v>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>1120051</t>
+        </is>
       </c>
     </row>
     <row r="68">
-      <c r="B68" t="n">
-        <v>1120030</v>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1120032</t>
+        </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1120052</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1130021</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1130041</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1130022</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>1130042</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1130023</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1130043</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1130024</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1130044</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1130025</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1130045</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1130026</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>1130046</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1130027</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>1130047</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1130028</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>1130048</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1130029</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>1130049</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1130030</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1130050</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1130031</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1130051</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1130032</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1130052</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>10017</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>1150041</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1150022</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
           <t>Minion</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>1120050</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" t="n">
-        <v>1120031</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Minion</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>1120051</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" t="n">
-        <v>1120032</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>1120052</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" t="n">
-        <v>1130021</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Elite</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>1130041</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" t="n">
-        <v>1130022</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>1130042</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="B73" t="n">
-        <v>1130023</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Elite</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>1130043</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" t="n">
-        <v>1130024</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Elite</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>1130044</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" t="n">
-        <v>1130025</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Elite</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>1130045</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" t="n">
-        <v>1130026</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>1130046</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="B77" t="n">
-        <v>1130027</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>1130047</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" t="n">
-        <v>1130028</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Elite</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>1130048</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="B79" t="n">
-        <v>1130029</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>1130049</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="B80" t="n">
-        <v>1130030</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Elite</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>1130050</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="B81" t="n">
-        <v>1130031</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Elite</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>1130051</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="B82" t="n">
-        <v>1130032</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Elite</t>
-        </is>
-      </c>
       <c r="D82" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E82" t="n">
-        <v>1130052</v>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>1150042</t>
+        </is>
       </c>
     </row>
     <row r="83">
-      <c r="B83" t="n">
-        <v>1140021</v>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1150023</t>
+        </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -1963,17 +2363,19 @@
           <t>100</t>
         </is>
       </c>
-      <c r="E83" t="n">
-        <v>1140041</v>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>1150043</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="B84" t="n">
-        <v>1140022</v>
+        <v>1020002</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -1982,16 +2384,16 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1140042</v>
+        <v>1020010</v>
       </c>
     </row>
     <row r="85">
       <c r="B85" t="n">
-        <v>1140023</v>
+        <v>1140021</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Minion</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2000,12 +2402,12 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1140043</v>
+        <v>1140041</v>
       </c>
     </row>
     <row r="86">
       <c r="B86" t="n">
-        <v>1140024</v>
+        <v>1140022</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -2018,12 +2420,12 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1140044</v>
+        <v>1140042</v>
       </c>
     </row>
     <row r="87">
       <c r="B87" t="n">
-        <v>1140025</v>
+        <v>1140023</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -2036,12 +2438,12 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1140045</v>
+        <v>1140043</v>
       </c>
     </row>
     <row r="88">
       <c r="B88" t="n">
-        <v>1140026</v>
+        <v>1140024</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -2054,12 +2456,12 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1140046</v>
+        <v>1140044</v>
       </c>
     </row>
     <row r="89">
       <c r="B89" t="n">
-        <v>1140027</v>
+        <v>1140025</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -2072,12 +2474,12 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1140047</v>
+        <v>1140045</v>
       </c>
     </row>
     <row r="90">
       <c r="B90" t="n">
-        <v>1140028</v>
+        <v>1140026</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -2090,12 +2492,12 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1140048</v>
+        <v>1140046</v>
       </c>
     </row>
     <row r="91">
       <c r="B91" t="n">
-        <v>1140029</v>
+        <v>1140027</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -2108,12 +2510,12 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1140049</v>
+        <v>1140047</v>
       </c>
     </row>
     <row r="92">
       <c r="B92" t="n">
-        <v>1140030</v>
+        <v>1140028</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -2126,12 +2528,12 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1140050</v>
+        <v>1140048</v>
       </c>
     </row>
     <row r="93">
       <c r="B93" t="n">
-        <v>10016</v>
+        <v>1140029</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -2144,16 +2546,16 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1140051</v>
+        <v>1140049</v>
       </c>
     </row>
     <row r="94">
       <c r="B94" t="n">
-        <v>1140032</v>
+        <v>1140030</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2162,16 +2564,16 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1140052</v>
+        <v>1140050</v>
       </c>
     </row>
     <row r="95">
       <c r="B95" t="n">
-        <v>10017</v>
+        <v>10016</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2180,16 +2582,16 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1150041</v>
+        <v>1140051</v>
       </c>
     </row>
     <row r="96">
       <c r="B96" t="n">
-        <v>1150022</v>
+        <v>1140032</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Minion</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -2198,16 +2600,16 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1150042</v>
+        <v>1140052</v>
       </c>
     </row>
     <row r="97">
       <c r="B97" t="n">
-        <v>1150023</v>
+        <v>1030002</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -2216,10 +2618,15 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1150043</v>
+        <v>1030010</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="C8:C1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Normal, Minion, Elite, Boss" promptTitle="EnemyRank enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"Normal,Minion,Elite,Boss"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>